--- a/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497601708649</v>
+        <v>10.84497636939199</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890708438512</v>
+        <v>37.78907207145167</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.992408060273283</v>
+        <v>6.542366701100745</v>
       </c>
       <c r="C2" t="n">
-        <v>4.749695393146069</v>
+        <v>7.855945129382977</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09677641655971</v>
+        <v>22.94933433447344</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.85017781634451</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="C3" t="n">
-        <v>24.00373136883452</v>
+        <v>27.26804248545516</v>
       </c>
       <c r="D3" t="n">
-        <v>74.85335371029805</v>
+        <v>60.25967408666923</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.65301075870693</v>
+        <v>39.38575439897354</v>
       </c>
       <c r="C4" t="n">
-        <v>77.25274509947727</v>
+        <v>40.87899265713293</v>
       </c>
       <c r="D4" t="n">
-        <v>98.14531799355365</v>
+        <v>80.97945938479815</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.43791020048565</v>
+        <v>49.70097752749479</v>
       </c>
       <c r="C5" t="n">
-        <v>129.590696960579</v>
+        <v>53.4070751110265</v>
       </c>
       <c r="D5" t="n">
-        <v>73.75379628154164</v>
+        <v>60.47565858160353</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>48.22148373719484</v>
       </c>
       <c r="C6" t="n">
-        <v>130.5763716556428</v>
+        <v>58.84792088796232</v>
       </c>
       <c r="D6" t="n">
-        <v>48.74475526355839</v>
+        <v>44.59883470852411</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.0279973240002</v>
+        <v>34.43480072645687</v>
       </c>
       <c r="C7" t="n">
-        <v>95.99823576436586</v>
+        <v>52.46067032413256</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.27799883121787</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="C8" t="n">
-        <v>59.91606239018283</v>
+        <v>40.97324043674063</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669488440372094</v>
+        <v>7.745979487647731</v>
       </c>
       <c r="C21" t="n">
-        <v>92.99254733951163</v>
+        <v>97.79299103155262</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669488440372094</v>
+        <v>8.714226923603698</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.96884611537136</v>
+        <v>10.06782270705104</v>
       </c>
       <c r="C2" t="n">
-        <v>3.651119712093887</v>
+        <v>6.60519855417254</v>
       </c>
       <c r="D2" t="n">
-        <v>26.52289597793183</v>
+        <v>19.06063167795183</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.5927799913826</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="C3" t="n">
-        <v>21.05848825609408</v>
+        <v>29.00573592197201</v>
       </c>
       <c r="D3" t="n">
-        <v>73.98450699203964</v>
+        <v>63.95595419315846</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.90826516181109</v>
+        <v>37.8414652601933</v>
       </c>
       <c r="C4" t="n">
-        <v>68.66343443502191</v>
+        <v>55.18600195112171</v>
       </c>
       <c r="D4" t="n">
-        <v>110.895275428607</v>
+        <v>90.81951662446394</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.4385320952914</v>
+        <v>55.02695882303374</v>
       </c>
       <c r="C5" t="n">
-        <v>134.204911170539</v>
+        <v>65.11441648416971</v>
       </c>
       <c r="D5" t="n">
-        <v>88.45546815263762</v>
+        <v>75.07915568227483</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.06805335789186</v>
+        <v>57.88188114698346</v>
       </c>
       <c r="C6" t="n">
-        <v>165.4745572985042</v>
+        <v>71.68819911180636</v>
       </c>
       <c r="D6" t="n">
-        <v>59.16993413495527</v>
+        <v>52.44790760397736</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.64599965605695</v>
+        <v>46.23246288839079</v>
       </c>
       <c r="C7" t="n">
-        <v>137.3798832460731</v>
+        <v>69.58824077242241</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.45733986592554</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>41.3796839862988</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
+        <v>34.30717352490479</v>
+      </c>
+      <c r="D10" t="n">
         <v>35.44600086183109</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.844717705763093</v>
+        <v>7.946214584660295</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0007404616998</v>
+        <v>107.273896892914</v>
       </c>
       <c r="D21" t="n">
-        <v>8.825307418983481</v>
+        <v>9.932768230825369</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.029133635957916</v>
+        <v>10.6352728801057</v>
       </c>
       <c r="C2" t="n">
-        <v>9.947067739428682</v>
+        <v>6.696501090667494</v>
       </c>
       <c r="D2" t="n">
-        <v>33.96159833300991</v>
+        <v>32.54788163889451</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.99038781160256</v>
+        <v>27.15514149946678</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7450897542611</v>
+        <v>27.13059780686061</v>
       </c>
       <c r="D3" t="n">
-        <v>76.28179661997716</v>
+        <v>63.91668428498858</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.54640116957152</v>
+        <v>38.30092318578082</v>
       </c>
       <c r="C4" t="n">
-        <v>60.69949705817179</v>
+        <v>63.21375292874787</v>
       </c>
       <c r="D4" t="n">
-        <v>118.182788637231</v>
+        <v>99.49816633000574</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.40202750378502</v>
+        <v>56.42594930158544</v>
       </c>
       <c r="C5" t="n">
-        <v>129.2225415714864</v>
+        <v>83.03131208667401</v>
       </c>
       <c r="D5" t="n">
-        <v>103.7216449536755</v>
+        <v>89.04451677518571</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.39385472698156</v>
+        <v>65.65045073068846</v>
       </c>
       <c r="C6" t="n">
-        <v>186.002901794305</v>
+        <v>86.09829191474104</v>
       </c>
       <c r="D6" t="n">
-        <v>69.35360307110744</v>
+        <v>62.06805335789186</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>59.34763046942393</v>
+        <v>57.13182590093888</v>
       </c>
       <c r="C7" t="n">
-        <v>178.5818708979033</v>
+        <v>86.23671834103982</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.22082078466007</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="C8" t="n">
-        <v>128.4273259310465</v>
+        <v>73.01748550335651</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C9" t="n">
-        <v>77.98905587766234</v>
+        <v>55.24687030878498</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>6.04167537193487</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.556291095409447</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>37.10122749119121</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.77770841267949</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.00426129693402</v>
+        <v>8.132880073823024</v>
       </c>
       <c r="C21" t="n">
-        <v>109.058060170726</v>
+        <v>116.910151061206</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00532662116752</v>
+        <v>11.18271010150666</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.341910242985147</v>
+        <v>9.494482047770903</v>
       </c>
       <c r="C2" t="n">
-        <v>6.842781498600268</v>
+        <v>4.285328729037327</v>
       </c>
       <c r="D2" t="n">
-        <v>27.90126975469435</v>
+        <v>25.88475997017141</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.02184479586747</v>
+        <v>30.82687791334985</v>
       </c>
       <c r="C3" t="n">
-        <v>32.46639657944202</v>
+        <v>40.27129082820417</v>
       </c>
       <c r="D3" t="n">
-        <v>83.53200341583987</v>
+        <v>73.14020396638738</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.009662912789</v>
+        <v>27.10801760966293</v>
       </c>
       <c r="C4" t="n">
-        <v>97.13706310129216</v>
+        <v>79.06505136151688</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4177861914445</v>
+        <v>97.96663991138071</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.07355862902306</v>
+        <v>36.98734475749859</v>
       </c>
       <c r="C5" t="n">
-        <v>111.133840120739</v>
+        <v>51.44357970253288</v>
       </c>
       <c r="D5" t="n">
-        <v>69.31138791982482</v>
+        <v>62.73367830137119</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.8302651248191</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>117.6153384641764</v>
+        <v>56.79508643838223</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>90.30900781825558</v>
+        <v>51.3228247349105</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>57.41260574435346</v>
+        <v>40.72289477215769</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.37623035490478</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.98146996680633</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>76.66467822463341</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.116869034534376</v>
+        <v>5.571418221600648</v>
       </c>
       <c r="C2" t="n">
-        <v>3.89361139504285</v>
+        <v>2.371902453460294</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53128973891355</v>
+        <v>17.64593323613217</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.2280118137593</v>
+        <v>33.2567034813607</v>
       </c>
       <c r="C3" t="n">
-        <v>30.16419821298325</v>
+        <v>27.98471830955533</v>
       </c>
       <c r="D3" t="n">
-        <v>87.13010875190442</v>
+        <v>76.91502388921636</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.14700978039232</v>
+        <v>41.88724754939441</v>
       </c>
       <c r="C4" t="n">
-        <v>92.97641633069418</v>
+        <v>92.49143296479625</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8359129024624</v>
+        <v>111.9035303208684</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.27053006467818</v>
+        <v>41.13522880794136</v>
       </c>
       <c r="C5" t="n">
-        <v>143.5806017460961</v>
+        <v>98.2238578098934</v>
       </c>
       <c r="D5" t="n">
-        <v>87.3264582927538</v>
+        <v>78.9079717288374</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.63279496754524</v>
+        <v>42.34474197957343</v>
       </c>
       <c r="C6" t="n">
-        <v>147.1198022199058</v>
+        <v>70.76241102670161</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>119.7133333081518</v>
+        <v>65.87527095496098</v>
       </c>
       <c r="D7" t="n">
         <v>31.32069700858599</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>77.60715602071035</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.74995743505333</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.210135066437823</v>
+        <v>6.14377713317654</v>
       </c>
       <c r="C2" t="n">
-        <v>10.09531164276995</v>
+        <v>4.69079053089126</v>
       </c>
       <c r="D2" t="n">
-        <v>27.89341577306038</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.78774687390022</v>
+        <v>25.83469083725482</v>
       </c>
       <c r="C3" t="n">
-        <v>22.12859325372311</v>
+        <v>17.40147805777471</v>
       </c>
       <c r="D3" t="n">
-        <v>83.38474126020284</v>
+        <v>73.21874378272712</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.83016731382786</v>
+        <v>53.84591633482481</v>
       </c>
       <c r="C4" t="n">
-        <v>83.91488502049611</v>
+        <v>80.13711985455438</v>
       </c>
       <c r="D4" t="n">
-        <v>139.2412768933251</v>
+        <v>124.5641487148353</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.86082247683777</v>
+        <v>52.00808463247479</v>
       </c>
       <c r="C5" t="n">
-        <v>158.5277105432537</v>
+        <v>137.6410281354028</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7040145527281</v>
+        <v>100.04009106275</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.99884799250906</v>
+        <v>49.34853010167018</v>
       </c>
       <c r="C6" t="n">
-        <v>184.7148488063332</v>
+        <v>113.3486629415197</v>
       </c>
       <c r="D6" t="n">
-        <v>54.78250364467628</v>
+        <v>53.81646390369741</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.09355343600648</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>163.5503317981804</v>
+        <v>84.97909953189966</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="C8" t="n">
-        <v>114.1576230498191</v>
+        <v>70.01333752836128</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>52.02968308196819</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.48354395430394</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.17006333701295</v>
+        <v>3.552944941669207</v>
       </c>
       <c r="C2" t="n">
-        <v>4.728096943652639</v>
+        <v>2.047925711058846</v>
       </c>
       <c r="D2" t="n">
-        <v>19.44056803949534</v>
+        <v>11.92430761578176</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.46377013149877</v>
+        <v>26.12921514852886</v>
       </c>
       <c r="C3" t="n">
-        <v>30.9790488075081</v>
+        <v>18.98700060013331</v>
       </c>
       <c r="D3" t="n">
-        <v>87.34609324683872</v>
+        <v>73.02730298039899</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.6800009728071</v>
+        <v>59.84439480777282</v>
       </c>
       <c r="C4" t="n">
-        <v>82.40888404218151</v>
+        <v>73.4239290529147</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9281814911284</v>
+        <v>133.7022563459646</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.94703634836225</v>
+        <v>54.60971604872884</v>
       </c>
       <c r="C5" t="n">
-        <v>183.7095391571844</v>
+        <v>160.0494194848363</v>
       </c>
       <c r="D5" t="n">
-        <v>114.6190444708151</v>
+        <v>110.7411410390402</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.50574860306991</v>
+        <v>44.47807974090175</v>
       </c>
       <c r="C6" t="n">
-        <v>218.1639748377262</v>
+        <v>144.5839478998363</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>52.85042416271855</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>12.27675504160636</v>
       </c>
       <c r="C7" t="n">
-        <v>162.7718058687126</v>
+        <v>91.0875337477233</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>81.77958376375931</v>
+        <v>62.33607048115122</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.632867416340698</v>
+        <v>6.189919275276139</v>
       </c>
       <c r="C2" t="n">
-        <v>7.985535826343555</v>
+        <v>2.091122610045706</v>
       </c>
       <c r="D2" t="n">
-        <v>16.44918278465531</v>
+        <v>10.68730550843078</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.39166058073225</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C3" t="n">
-        <v>24.62223242251001</v>
+        <v>12.9885221271853</v>
       </c>
       <c r="D3" t="n">
-        <v>83.65472187887072</v>
+        <v>66.07162049581034</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.99157484795184</v>
+        <v>55.40296819376024</v>
       </c>
       <c r="C4" t="n">
-        <v>80.60934050029711</v>
+        <v>60.35490361398116</v>
       </c>
       <c r="D4" t="n">
-        <v>156.4071355020806</v>
+        <v>139.3433786545668</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.16350386938205</v>
+        <v>71.02944640225674</v>
       </c>
       <c r="C5" t="n">
-        <v>170.5050325350648</v>
+        <v>149.201107352909</v>
       </c>
       <c r="D5" t="n">
-        <v>135.8493385751524</v>
+        <v>132.3150468398639</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.97747052719389</v>
+        <v>57.72087452348698</v>
       </c>
       <c r="C6" t="n">
-        <v>252.6193922659723</v>
+        <v>197.7563853095478</v>
       </c>
       <c r="D6" t="n">
-        <v>70.88316599432396</v>
+        <v>70.68190771495337</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>26.94897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>227.6888910643287</v>
+        <v>146.3029881299724</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>136.6887328622834</v>
+        <v>88.78926237208152</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
         <v>21.91359050649305</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>36.36098972218912</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.258420630395164</v>
+        <v>4.202861921880595</v>
       </c>
       <c r="C2" t="n">
-        <v>4.399211462729958</v>
+        <v>2.385646921319749</v>
       </c>
       <c r="D2" t="n">
-        <v>12.03917209717864</v>
+        <v>7.994371555681777</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.85660808191773</v>
+        <v>20.43016972537612</v>
       </c>
       <c r="C3" t="n">
-        <v>27.7638250760998</v>
+        <v>10.82867717784232</v>
       </c>
       <c r="D3" t="n">
-        <v>78.93251542144355</v>
+        <v>60.75054793879263</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.77162230447154</v>
+        <v>49.35343884019141</v>
       </c>
       <c r="C4" t="n">
-        <v>74.55981114672825</v>
+        <v>48.51109930994765</v>
       </c>
       <c r="D4" t="n">
-        <v>162.8650719006161</v>
+        <v>141.1046340359856</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.00490270965058</v>
+        <v>78.71162218798803</v>
       </c>
       <c r="C5" t="n">
-        <v>168.0015758892355</v>
+        <v>138.4509699914065</v>
       </c>
       <c r="D5" t="n">
-        <v>150.4282919832175</v>
+        <v>147.753029489145</v>
       </c>
     </row>
     <row r="6">
@@ -3324,10 +3324,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.91333813124836</v>
+        <v>69.23284810348508</v>
       </c>
       <c r="C6" t="n">
-        <v>271.3364122474377</v>
+        <v>222.148888769264</v>
       </c>
       <c r="D6" t="n">
         <v>85.21275548551041</v>
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>28.086820070797</v>
       </c>
       <c r="C7" t="n">
-        <v>275.7778388614503</v>
+        <v>198.2845655744325</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>180.3323270545754</v>
+        <v>120.3328161095315</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>61.57030727183869</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.89401230567035</v>
+        <v>6.013204688511713</v>
       </c>
       <c r="C2" t="n">
-        <v>3.281982575297087</v>
+        <v>5.987679248201297</v>
       </c>
       <c r="D2" t="n">
-        <v>23.44413517741383</v>
+        <v>8.026769229921921</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.02426595516569</v>
+        <v>17.33766445699867</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66364575253762</v>
+        <v>10.07764018409351</v>
       </c>
       <c r="D3" t="n">
-        <v>71.62831250184728</v>
+        <v>54.42318398492193</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.61999118966102</v>
+        <v>44.13348629671111</v>
       </c>
       <c r="C4" t="n">
-        <v>71.99450439553134</v>
+        <v>38.10948238345269</v>
       </c>
       <c r="D4" t="n">
-        <v>164.0137167145849</v>
+        <v>139.3944295351876</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.45865007546185</v>
+        <v>77.90168033198441</v>
       </c>
       <c r="C5" t="n">
-        <v>154.5761760336603</v>
+        <v>115.6253358676681</v>
       </c>
       <c r="D5" t="n">
-        <v>167.7315952705676</v>
+        <v>159.6321767105314</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75.19009317285472</v>
+        <v>84.68948395914687</v>
       </c>
       <c r="C6" t="n">
-        <v>270.6521340975777</v>
+        <v>222.148888769264</v>
       </c>
       <c r="D6" t="n">
-        <v>104.2517887139688</v>
+        <v>106.7071397222901</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.1059563032632</v>
+        <v>48.14883440708056</v>
       </c>
       <c r="C7" t="n">
-        <v>325.9628180071387</v>
+        <v>254.5180923259856</v>
       </c>
       <c r="D7" t="n">
-        <v>54.19738201294516</v>
+        <v>58.20978488020188</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>250.1787674732147</v>
+        <v>179.8316357254095</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C9" t="n">
-        <v>120.8109272414997</v>
+        <v>97.73592920088268</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>12.29148125717007</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>31.41199954508094</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.332493676570179</v>
+        <v>6.42357522888688</v>
       </c>
       <c r="C2" t="n">
-        <v>5.388813148610742</v>
+        <v>3.14257440129404</v>
       </c>
       <c r="D2" t="n">
-        <v>12.37885680284803</v>
+        <v>5.657812019574368</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.541163969218245</v>
+        <v>4.165555509119216</v>
       </c>
       <c r="C2" t="n">
-        <v>1.88986433067511</v>
+        <v>3.209333245182823</v>
       </c>
       <c r="D2" t="n">
-        <v>17.44271146135308</v>
+        <v>5.843362335677015</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.71211124294421</v>
+        <v>23.05143609571511</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25269437508571</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D3" t="n">
-        <v>79.56574269068275</v>
+        <v>58.22254760035709</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.10567856582271</v>
+        <v>59.99754744963532</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2256413788526</v>
+        <v>56.5133248472634</v>
       </c>
       <c r="D4" t="n">
-        <v>167.3575493952495</v>
+        <v>144.1166359926148</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.63868545377073</v>
+        <v>52.03262832508096</v>
       </c>
       <c r="C5" t="n">
-        <v>230.4161861867264</v>
+        <v>180.7888397370502</v>
       </c>
       <c r="D5" t="n">
-        <v>151.9009135395877</v>
+        <v>149.2256510455152</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.2717484920939</v>
+        <v>29.86672865859647</v>
       </c>
       <c r="C6" t="n">
-        <v>265.0974055869493</v>
+        <v>219.8947960403134</v>
       </c>
       <c r="D6" t="n">
-        <v>82.11337798320324</v>
+        <v>86.29955019411163</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>175.9468600597048</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>89.03960803666446</v>
+        <v>72.01610284502478</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>26.11939767148639</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.56280347644068</v>
+        <v>6.394122797759476</v>
       </c>
       <c r="C2" t="n">
-        <v>4.12432210554085</v>
+        <v>2.284526907782328</v>
       </c>
       <c r="D2" t="n">
-        <v>13.83184340513331</v>
+        <v>12.69988830213674</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81166867170063</v>
+        <v>13.64138435050943</v>
       </c>
       <c r="C3" t="n">
-        <v>13.57757074973339</v>
+        <v>8.040513697781376</v>
       </c>
       <c r="D3" t="n">
-        <v>13.53339210304228</v>
+        <v>8.114144775599888</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39735012528342</v>
+        <v>13.39939065317139</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13906830295437</v>
+        <v>70.14975106660316</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576158838268637</v>
+        <v>1.576398900373104</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.21111681414207</v>
+        <v>5.535093556543517</v>
       </c>
       <c r="C2" t="n">
-        <v>8.315403054970485</v>
+        <v>2.721404636172158</v>
       </c>
       <c r="D2" t="n">
-        <v>27.7490988605361</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.73651606683013</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="C3" t="n">
-        <v>15.14345833800705</v>
+        <v>8.595201150680825</v>
       </c>
       <c r="D3" t="n">
-        <v>21.87824758914017</v>
+        <v>16.81733817374786</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.81974363751286</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="C4" t="n">
-        <v>21.24992905842221</v>
+        <v>12.99244911800229</v>
       </c>
       <c r="D4" t="n">
-        <v>22.15608218944201</v>
+        <v>19.32275831498572</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43952663739352</v>
+        <v>15.44611234051997</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13630650335332</v>
+        <v>86.17304779447983</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250426660503899</v>
+        <v>3.251813124319994</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.296528864411543</v>
+        <v>5.372123437638546</v>
       </c>
       <c r="C2" t="n">
-        <v>6.346998907955629</v>
+        <v>2.874557278034661</v>
       </c>
       <c r="D2" t="n">
-        <v>26.20382797405162</v>
+        <v>20.49594682156066</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.392282475538</v>
+        <v>19.15880644837651</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58434517267188</v>
+        <v>9.827294519510573</v>
       </c>
       <c r="D3" t="n">
-        <v>38.99992755120454</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.23710958500477</v>
+        <v>28.05245890114836</v>
       </c>
       <c r="C4" t="n">
-        <v>31.06446085777758</v>
+        <v>18.11029990024091</v>
       </c>
       <c r="D4" t="n">
-        <v>28.14179794223482</v>
+        <v>23.22815068247953</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.09499284760047</v>
+        <v>13.94081740030471</v>
       </c>
       <c r="C5" t="n">
-        <v>24.66641106920112</v>
+        <v>16.1742934274662</v>
       </c>
       <c r="D5" t="n">
-        <v>30.63052837250049</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73003123158003</v>
+        <v>16.74742589742382</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0531905126382</v>
+        <v>102.1592979742853</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182507807895008</v>
+        <v>5.024227769227148</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.729299675535137</v>
+        <v>5.853179812719484</v>
       </c>
       <c r="C2" t="n">
-        <v>12.16189056020949</v>
+        <v>3.861213720802705</v>
       </c>
       <c r="D2" t="n">
-        <v>27.6401248653647</v>
+        <v>24.49460522095792</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.58586669972387</v>
+        <v>18.80046853632642</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01984024272996</v>
+        <v>10.60778394438679</v>
       </c>
       <c r="D3" t="n">
-        <v>50.24093876483052</v>
+        <v>36.00559705325177</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.70482240285375</v>
+        <v>33.27241144462865</v>
       </c>
       <c r="C4" t="n">
-        <v>49.46830332158828</v>
+        <v>21.62004794292326</v>
       </c>
       <c r="D4" t="n">
-        <v>40.63650097418398</v>
+        <v>30.51566389110361</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>28.2252464970958</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31332605303754</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="D5" t="n">
-        <v>33.45305302221007</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.61764247915826</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>26.04282135055514</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05204904208805</v>
+        <v>18.08664517696571</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7681294650506</v>
+        <v>117.9938280592525</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017349680696017</v>
+        <v>6.890150543605983</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.466191290796993</v>
+        <v>6.453027660014286</v>
       </c>
       <c r="C2" t="n">
-        <v>8.850455553784995</v>
+        <v>3.91815508764902</v>
       </c>
       <c r="D2" t="n">
-        <v>25.14059521035232</v>
+        <v>22.92577238957152</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89649988489336</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C3" t="n">
-        <v>35.21038141281186</v>
+        <v>12.45346962837079</v>
       </c>
       <c r="D3" t="n">
-        <v>56.51430659496764</v>
+        <v>44.50262343350792</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.19284882285566</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="C4" t="n">
-        <v>46.99233561147783</v>
+        <v>20.53521672973053</v>
       </c>
       <c r="D4" t="n">
-        <v>48.71530283243098</v>
+        <v>36.43756604312036</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.84513020910304</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>50.97724954301564</v>
+        <v>24.91184799526282</v>
       </c>
       <c r="D5" t="n">
-        <v>32.25041208450773</v>
+        <v>28.81429511964389</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>14.24908617943821</v>
       </c>
       <c r="C6" t="n">
-        <v>31.79880814055419</v>
+        <v>21.21262264566084</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>19.04394196697963</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053320714773454</v>
+        <v>7.075689143041189</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12488170100113</v>
+        <v>67.21904685889129</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408325446733409</v>
+        <v>5.306766857280892</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.403940274801944</v>
+        <v>5.811946409141117</v>
       </c>
       <c r="C2" t="n">
-        <v>6.933102287390975</v>
+        <v>5.519385593275567</v>
       </c>
       <c r="D2" t="n">
-        <v>28.39214360681775</v>
+        <v>19.21771131063131</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.07245370813179</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80786485407066</v>
+        <v>14.40714755982194</v>
       </c>
       <c r="D3" t="n">
-        <v>63.9755891472434</v>
+        <v>53.4954324044087</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.83771819582557</v>
+        <v>31.72812230584842</v>
       </c>
       <c r="C4" t="n">
-        <v>72.95170840717199</v>
+        <v>27.60576369571606</v>
       </c>
       <c r="D4" t="n">
-        <v>66.55758560941251</v>
+        <v>51.71454206890498</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.60093707265284</v>
+        <v>33.13398501832986</v>
       </c>
       <c r="C5" t="n">
-        <v>72.96839811814419</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="D5" t="n">
-        <v>43.63868545377073</v>
+        <v>36.64373306101221</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.11452999069417</v>
+        <v>25.64030479181395</v>
       </c>
       <c r="C6" t="n">
-        <v>60.73974871404592</v>
+        <v>32.60384125803657</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.15131231964102</v>
+        <v>12.6360747013607</v>
       </c>
       <c r="C7" t="n">
-        <v>34.7941203862112</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>22.78145547704723</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27325812409267</v>
+        <v>7.308622516777824</v>
       </c>
       <c r="C21" t="n">
-        <v>75.46005303746145</v>
+        <v>77.65411424076439</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454943593069502</v>
+        <v>6.395044702180596</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.760314691443536</v>
+        <v>5.177737392197677</v>
       </c>
       <c r="C2" t="n">
-        <v>4.913647259755286</v>
+        <v>8.319330045787471</v>
       </c>
       <c r="D2" t="n">
-        <v>25.41646631524567</v>
+        <v>20.88471891244239</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.95817006381166</v>
+        <v>20.64615422031042</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11511082777091</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="D3" t="n">
-        <v>71.84429699678158</v>
+        <v>56.710656135817</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.77238306799753</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="C4" t="n">
-        <v>81.1964256274367</v>
+        <v>32.62151271671301</v>
       </c>
       <c r="D4" t="n">
-        <v>83.68515605770236</v>
+        <v>67.74451858384691</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.68210333693584</v>
+        <v>41.60155896745859</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6240920780566</v>
+        <v>44.20319038371264</v>
       </c>
       <c r="D5" t="n">
-        <v>57.67767762450012</v>
+        <v>47.22206457427158</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>90.00270253453061</v>
+        <v>44.67933802027235</v>
       </c>
       <c r="D6" t="n">
-        <v>40.49316580936395</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>22.81679839440012</v>
       </c>
       <c r="C7" t="n">
-        <v>63.59957977651686</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>35.549084370777</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47892407446375</v>
+        <v>7.532843727501826</v>
       </c>
       <c r="C21" t="n">
-        <v>84.13789583771718</v>
+        <v>87.56930833220872</v>
       </c>
       <c r="D21" t="n">
-        <v>6.544058565155781</v>
+        <v>7.532843727501826</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636939199</v>
+        <v>10.84497628244782</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907207145167</v>
+        <v>37.7890717684967</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.542366701100745</v>
+        <v>4.660356352059609</v>
       </c>
       <c r="C2" t="n">
-        <v>7.855945129382977</v>
+        <v>5.201299337099601</v>
       </c>
       <c r="D2" t="n">
-        <v>22.94933433447344</v>
+        <v>34.69103687726529</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1146278016854</v>
+        <v>14.60840583919254</v>
       </c>
       <c r="C3" t="n">
-        <v>27.26804248545516</v>
+        <v>28.77502521147402</v>
       </c>
       <c r="D3" t="n">
-        <v>60.25967408666923</v>
+        <v>86.9239417340126</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.38575439897354</v>
+        <v>31.97061398879738</v>
       </c>
       <c r="C4" t="n">
-        <v>40.87899265713293</v>
+        <v>83.2895117328909</v>
       </c>
       <c r="D4" t="n">
-        <v>80.97945938479815</v>
+        <v>116.408770535657</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.70097752749479</v>
+        <v>39.09810232162923</v>
       </c>
       <c r="C5" t="n">
-        <v>53.4070751110265</v>
+        <v>130.744250513069</v>
       </c>
       <c r="D5" t="n">
-        <v>60.47565858160353</v>
+        <v>81.28870991163591</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.22148373719484</v>
+        <v>36.54850353370026</v>
       </c>
       <c r="C6" t="n">
-        <v>58.84792088796232</v>
+        <v>141.4040670857809</v>
       </c>
       <c r="D6" t="n">
-        <v>44.59883470852411</v>
+        <v>50.95859633663495</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.43480072645687</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>52.46067032413256</v>
+        <v>124.6240353247943</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.35868206941536</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>40.97324043674063</v>
+        <v>83.53200341583985</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.653124265231384</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.745979487647731</v>
+        <v>7.653500112812806</v>
       </c>
       <c r="C21" t="n">
-        <v>97.79299103155262</v>
+        <v>92.79868886785528</v>
       </c>
       <c r="D21" t="n">
-        <v>8.714226923603698</v>
+        <v>7.653500112812806</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.06782270705104</v>
+        <v>5.20817157102933</v>
       </c>
       <c r="C2" t="n">
-        <v>6.60519855417254</v>
+        <v>7.63014315740621</v>
       </c>
       <c r="D2" t="n">
-        <v>19.06063167795183</v>
+        <v>28.25077193740622</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7296027751714</v>
+        <v>14.92256510455152</v>
       </c>
       <c r="C3" t="n">
-        <v>29.00573592197201</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="D3" t="n">
-        <v>63.95595419315846</v>
+        <v>92.29410167624265</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8414652601933</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>55.18600195112171</v>
+        <v>77.64838942428872</v>
       </c>
       <c r="D4" t="n">
-        <v>90.81951662446394</v>
+        <v>128.584405563726</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.02695882303374</v>
+        <v>42.65693774952392</v>
       </c>
       <c r="C5" t="n">
-        <v>65.11441648416971</v>
+        <v>139.7517856995335</v>
       </c>
       <c r="D5" t="n">
-        <v>75.07915568227483</v>
+        <v>100.7027707631166</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.88188114698346</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>71.68819911180636</v>
+        <v>171.5928089913703</v>
       </c>
       <c r="D6" t="n">
-        <v>52.44790760397736</v>
+        <v>61.62528514327655</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.23246288839079</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="C7" t="n">
-        <v>69.58824077242241</v>
+        <v>159.4780423209646</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>44.73529763941441</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.20561154301086</v>
+        <v>18.85937339858123</v>
       </c>
       <c r="C8" t="n">
-        <v>55.99398031171682</v>
+        <v>120.5831617741145</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>70.88905648054941</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.946214584660295</v>
+        <v>7.823669950991503</v>
       </c>
       <c r="C21" t="n">
-        <v>107.273896892914</v>
+        <v>100.7297506190156</v>
       </c>
       <c r="D21" t="n">
-        <v>9.932768230825369</v>
+        <v>8.801628694865441</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.6352728801057</v>
+        <v>5.902267197931824</v>
       </c>
       <c r="C2" t="n">
-        <v>6.696501090667494</v>
+        <v>7.691011515069513</v>
       </c>
       <c r="D2" t="n">
-        <v>32.54788163889451</v>
+        <v>23.79756435094269</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.15514149946678</v>
+        <v>15.63433219013045</v>
       </c>
       <c r="C3" t="n">
-        <v>27.13059780686061</v>
+        <v>26.44337441388784</v>
       </c>
       <c r="D3" t="n">
-        <v>63.91668428498858</v>
+        <v>92.25974050659401</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.30092318578082</v>
+        <v>28.4098150654942</v>
       </c>
       <c r="C4" t="n">
-        <v>63.21375292874787</v>
+        <v>69.36538404355839</v>
       </c>
       <c r="D4" t="n">
-        <v>99.49816633000574</v>
+        <v>140.7089897111741</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.42594930158544</v>
+        <v>43.09872421643498</v>
       </c>
       <c r="C5" t="n">
-        <v>83.03131208667401</v>
+        <v>139.3590866178347</v>
       </c>
       <c r="D5" t="n">
-        <v>89.04451677518571</v>
+        <v>116.3616466458532</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.65045073068846</v>
+        <v>48.90576188705487</v>
       </c>
       <c r="C6" t="n">
-        <v>86.09829191474104</v>
+        <v>192.765179981157</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06805335789186</v>
+        <v>74.7070733023653</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.13182590093888</v>
+        <v>40.3036885024443</v>
       </c>
       <c r="C7" t="n">
-        <v>86.23671834103982</v>
+        <v>194.451822537053</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>49.76577287597506</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.88702656521616</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="C8" t="n">
-        <v>73.01748550335651</v>
+        <v>157.1336288032232</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.30156077611979</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>102.5062412958179</v>
       </c>
       <c r="D9" t="n">
-        <v>38.2734342500619</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>58.93431468593603</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.556291095409447</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>37.10122749119121</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>32.26022956155019</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.88498095434966</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>20.77770841267949</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.132880073823024</v>
+        <v>7.97843713680231</v>
       </c>
       <c r="C21" t="n">
-        <v>116.910151061206</v>
+        <v>107.7089013468312</v>
       </c>
       <c r="D21" t="n">
-        <v>11.18271010150666</v>
+        <v>9.973046421002888</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.494482047770903</v>
+        <v>5.446736263161304</v>
       </c>
       <c r="C2" t="n">
-        <v>4.285328729037327</v>
+        <v>5.352488483553611</v>
       </c>
       <c r="D2" t="n">
-        <v>25.88475997017141</v>
+        <v>19.92358790998477</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.82687791334985</v>
+        <v>19.03117924682442</v>
       </c>
       <c r="C3" t="n">
-        <v>40.27129082820417</v>
+        <v>40.65417243286042</v>
       </c>
       <c r="D3" t="n">
-        <v>73.14020396638738</v>
+        <v>100.7616756253714</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.10801760966293</v>
+        <v>20.70113209174825</v>
       </c>
       <c r="C4" t="n">
-        <v>79.06505136151688</v>
+        <v>106.8494931394059</v>
       </c>
       <c r="D4" t="n">
-        <v>97.96663991138071</v>
+        <v>133.6767309056542</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.98734475749859</v>
+        <v>27.53802310412304</v>
       </c>
       <c r="C5" t="n">
-        <v>51.44357970253288</v>
+        <v>115.1835494007571</v>
       </c>
       <c r="D5" t="n">
-        <v>62.73367830137119</v>
+        <v>75.91364123088462</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>24.99627829782805</v>
       </c>
       <c r="C6" t="n">
-        <v>56.79508643838223</v>
+        <v>128.0807689914474</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>32.76484788153306</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>51.3228247349105</v>
+        <v>110.4907953744573</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>40.72289477215769</v>
+        <v>75.52094214918588</v>
       </c>
       <c r="D8" t="n">
-        <v>28.20561154301086</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.37623035490478</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.98146996680633</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>76.66467822463341</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.571418221600648</v>
+        <v>3.308489763311751</v>
       </c>
       <c r="C2" t="n">
-        <v>2.371902453460294</v>
+        <v>2.627156856564465</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64593323613217</v>
+        <v>14.18723607407066</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.2567034813607</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="C3" t="n">
-        <v>27.98471830955533</v>
+        <v>31.38647410477053</v>
       </c>
       <c r="D3" t="n">
-        <v>76.91502388921636</v>
+        <v>95.76948854927636</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.88724754939441</v>
+        <v>27.31222113214627</v>
       </c>
       <c r="C4" t="n">
-        <v>92.49143296479625</v>
+        <v>108.202341475858</v>
       </c>
       <c r="D4" t="n">
-        <v>111.9035303208684</v>
+        <v>149.3621139764055</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.13522880794136</v>
+        <v>30.50780990946964</v>
       </c>
       <c r="C5" t="n">
-        <v>98.2238578098934</v>
+        <v>152.7353990881975</v>
       </c>
       <c r="D5" t="n">
-        <v>78.9079717288374</v>
+        <v>98.3956636581366</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.34474197957343</v>
+        <v>29.34345713223292</v>
       </c>
       <c r="C6" t="n">
-        <v>70.76241102670161</v>
+        <v>156.3374314150791</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>41.25794727097221</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>65.87527095496098</v>
+        <v>139.4759145946401</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>51.98844967838984</v>
+        <v>99.63757450400877</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.78145547704723</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.74995743505333</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>66.80105904006572</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.14377713317654</v>
+        <v>4.336379609658161</v>
       </c>
       <c r="C2" t="n">
-        <v>4.69079053089126</v>
+        <v>11.90270916628833</v>
       </c>
       <c r="D2" t="n">
-        <v>17.45252893839555</v>
+        <v>19.22360179685679</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.83469083725482</v>
+        <v>15.45270886484479</v>
       </c>
       <c r="C3" t="n">
-        <v>17.40147805777471</v>
+        <v>20.42035224833366</v>
       </c>
       <c r="D3" t="n">
-        <v>73.21874378272712</v>
+        <v>85.95201150680825</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.84591633482481</v>
+        <v>31.57496966398591</v>
       </c>
       <c r="C4" t="n">
-        <v>80.13711985455438</v>
+        <v>93.1806198531775</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5641487148353</v>
+        <v>161.0782910788869</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.00808463247479</v>
+        <v>35.31837366027901</v>
       </c>
       <c r="C5" t="n">
-        <v>137.6410281354028</v>
+        <v>176.5182372235765</v>
       </c>
       <c r="D5" t="n">
-        <v>100.04009106275</v>
+        <v>124.3874341280709</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.34853010167018</v>
+        <v>34.61642405174254</v>
       </c>
       <c r="C6" t="n">
-        <v>113.3486629415197</v>
+        <v>195.5022925805971</v>
       </c>
       <c r="D6" t="n">
-        <v>53.81646390369741</v>
+        <v>58.00263611460582</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.12969817461437</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="C7" t="n">
-        <v>84.97909953189966</v>
+        <v>180.0191495369206</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.52557917913731</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>70.01333752836128</v>
+        <v>137.6901155206152</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>79.43124325520091</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4164820107789</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.00617789032851</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.91916219754903</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>20.55288818840698</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.48354395430394</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.552944941669207</v>
+        <v>2.569233742013903</v>
       </c>
       <c r="C2" t="n">
-        <v>2.047925711058846</v>
+        <v>5.649958037940394</v>
       </c>
       <c r="D2" t="n">
-        <v>11.92430761578176</v>
+        <v>13.43325383720911</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.12921514852886</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>18.98700060013331</v>
+        <v>32.65292864324891</v>
       </c>
       <c r="D3" t="n">
-        <v>73.02730298039899</v>
+        <v>85.08316478854982</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.84439480777282</v>
+        <v>34.56144618030471</v>
       </c>
       <c r="C4" t="n">
-        <v>73.4239290529147</v>
+        <v>87.47568394379931</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7022563459646</v>
+        <v>169.9228561464464</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.60971604872884</v>
+        <v>36.88916998707391</v>
       </c>
       <c r="C5" t="n">
-        <v>160.0494194848363</v>
+        <v>206.9769597478339</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7411410390402</v>
+        <v>130.9406000539184</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.47807974090175</v>
+        <v>28.2566624236317</v>
       </c>
       <c r="C6" t="n">
-        <v>144.5839478998363</v>
+        <v>229.5954451059761</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>56.27181491201868</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.27675504160636</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>91.0875337477233</v>
+        <v>184.2112122340545</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>62.33607048115122</v>
+        <v>98.96998606512095</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>32.63820242768521</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.189919275276139</v>
+        <v>2.770492021384499</v>
       </c>
       <c r="C2" t="n">
-        <v>2.091122610045706</v>
+        <v>7.601672473983053</v>
       </c>
       <c r="D2" t="n">
-        <v>10.68730550843078</v>
+        <v>17.99641716654828</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.16371518689774</v>
+        <v>12.79217258633594</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9885221271853</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="D3" t="n">
-        <v>66.07162049581034</v>
+        <v>77.74460069930491</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.40296819376024</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C4" t="n">
-        <v>60.35490361398116</v>
+        <v>85.30602151741385</v>
       </c>
       <c r="D4" t="n">
-        <v>139.3433786545668</v>
+        <v>172.6285528193506</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.02944640225674</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>149.201107352909</v>
+        <v>185.9184714917398</v>
       </c>
       <c r="D5" t="n">
-        <v>132.3150468398639</v>
+        <v>155.1406809636022</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.72087452348698</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="C6" t="n">
-        <v>197.7563853095478</v>
+        <v>277.3339089726815</v>
       </c>
       <c r="D6" t="n">
-        <v>70.68190771495337</v>
+        <v>77.36368259005717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.94897448157494</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>146.3029881299724</v>
+        <v>246.0740803217588</v>
       </c>
       <c r="D7" t="n">
-        <v>41.9206269713388</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>88.78926237208152</v>
+        <v>156.4660403643354</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>64.5656195174957</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>36.36098972218912</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.202861921880595</v>
+        <v>1.827032477603314</v>
       </c>
       <c r="C2" t="n">
-        <v>2.385646921319749</v>
+        <v>4.778166076569226</v>
       </c>
       <c r="D2" t="n">
-        <v>7.994371555681777</v>
+        <v>13.44307131425157</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.43016972537612</v>
+        <v>11.50608309377262</v>
       </c>
       <c r="C3" t="n">
-        <v>10.82867717784232</v>
+        <v>28.57376693210342</v>
       </c>
       <c r="D3" t="n">
-        <v>60.75054793879263</v>
+        <v>75.00552460445631</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.35343884019141</v>
+        <v>30.40079940970673</v>
       </c>
       <c r="C4" t="n">
-        <v>48.51109930994765</v>
+        <v>80.41789969796898</v>
       </c>
       <c r="D4" t="n">
-        <v>141.1046340359856</v>
+        <v>172.7178918604371</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>78.71162218798803</v>
+        <v>46.55938487390499</v>
       </c>
       <c r="C5" t="n">
-        <v>138.4509699914065</v>
+        <v>179.8316357254095</v>
       </c>
       <c r="D5" t="n">
-        <v>147.753029489145</v>
+        <v>172.0758288618597</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.23284810348508</v>
+        <v>42.54600025894403</v>
       </c>
       <c r="C6" t="n">
-        <v>222.148888769264</v>
+        <v>299.9955912298107</v>
       </c>
       <c r="D6" t="n">
-        <v>85.21275548551041</v>
+        <v>91.53226545774713</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.086820070797</v>
+        <v>13.83380690054181</v>
       </c>
       <c r="C7" t="n">
-        <v>198.2845655744325</v>
+        <v>297.9358845463008</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>44.97484407925062</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>120.3328161095315</v>
+        <v>201.9455027635689</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>61.57030727183869</v>
+        <v>70.9999939711293</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.99868376159304</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.013204688511713</v>
+        <v>2.700787934382975</v>
       </c>
       <c r="C2" t="n">
-        <v>5.987679248201297</v>
+        <v>6.249805885235195</v>
       </c>
       <c r="D2" t="n">
-        <v>8.026769229921921</v>
+        <v>19.10579207234718</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.33766445699867</v>
+        <v>9.002626447943252</v>
       </c>
       <c r="C3" t="n">
-        <v>10.07764018409351</v>
+        <v>23.85156047467626</v>
       </c>
       <c r="D3" t="n">
-        <v>54.42318398492193</v>
+        <v>69.98879383575512</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.13348629671111</v>
+        <v>26.53369520267854</v>
       </c>
       <c r="C4" t="n">
-        <v>38.10948238345269</v>
+        <v>76.20620204675016</v>
       </c>
       <c r="D4" t="n">
-        <v>139.3944295351876</v>
+        <v>168.7997367727881</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>77.90168033198441</v>
+        <v>46.04396732917541</v>
       </c>
       <c r="C5" t="n">
-        <v>115.6253358676681</v>
+        <v>166.1607989437727</v>
       </c>
       <c r="D5" t="n">
-        <v>159.6321767105314</v>
+        <v>188.3482970597506</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.68948395914687</v>
+        <v>49.83154997215961</v>
       </c>
       <c r="C6" t="n">
-        <v>222.148888769264</v>
+        <v>295.6081607395316</v>
       </c>
       <c r="D6" t="n">
-        <v>106.7071397222901</v>
+        <v>114.1536960590021</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.14883440708056</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>254.5180923259856</v>
+        <v>354.5287309576081</v>
       </c>
       <c r="D7" t="n">
-        <v>58.20978488020188</v>
+        <v>55.21545438224911</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>179.8316357254095</v>
+        <v>272.8767743954009</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.771874679716245</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>97.73592920088268</v>
+        <v>133.568738658187</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.78145547704723</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31.41199954508094</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42357522888688</v>
+        <v>4.304963683122264</v>
       </c>
       <c r="C2" t="n">
-        <v>3.14257440129404</v>
+        <v>9.664324400605601</v>
       </c>
       <c r="D2" t="n">
-        <v>5.657812019574368</v>
+        <v>13.03270077387641</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.165555509119216</v>
+        <v>1.950732688338412</v>
       </c>
       <c r="C2" t="n">
-        <v>3.209333245182823</v>
+        <v>3.649156216685394</v>
       </c>
       <c r="D2" t="n">
-        <v>5.843362335677015</v>
+        <v>14.21374326208532</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.05143609571511</v>
+        <v>12.13931036301181</v>
       </c>
       <c r="C3" t="n">
-        <v>16.12520604225386</v>
+        <v>27.58220175081414</v>
       </c>
       <c r="D3" t="n">
-        <v>58.22254760035709</v>
+        <v>76.90029767365266</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.99754744963532</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>56.5133248472634</v>
+        <v>106.7091032176986</v>
       </c>
       <c r="D4" t="n">
-        <v>144.1166359926148</v>
+        <v>174.1983673984413</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.03262832508096</v>
+        <v>28.91246989006857</v>
       </c>
       <c r="C5" t="n">
-        <v>180.7888397370502</v>
+        <v>248.3576254818369</v>
       </c>
       <c r="D5" t="n">
-        <v>149.2256510455152</v>
+        <v>170.382314072034</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.86672865859647</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="C6" t="n">
-        <v>219.8947960403134</v>
+        <v>288.5641209615608</v>
       </c>
       <c r="D6" t="n">
-        <v>86.29955019411163</v>
+        <v>86.42030516173399</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>191.8766983088136</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.586905200690345</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>72.01610284502478</v>
+        <v>98.3858461810941</v>
       </c>
       <c r="D8" t="n">
-        <v>26.11939767148639</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6656249434793372</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>18.12502611580461</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.93314334511998</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.394122797759476</v>
+        <v>6.541384953396497</v>
       </c>
       <c r="C2" t="n">
-        <v>2.284526907782328</v>
+        <v>6.110397711232148</v>
       </c>
       <c r="D2" t="n">
-        <v>12.69988830213674</v>
+        <v>17.78632315783946</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.64138435050943</v>
+        <v>9.149888603580273</v>
       </c>
       <c r="C3" t="n">
-        <v>8.040513697781376</v>
+        <v>24.35225180384213</v>
       </c>
       <c r="D3" t="n">
-        <v>8.114144775599888</v>
+        <v>14.08317081742049</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39939065317139</v>
+        <v>13.39736695074953</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14975106660316</v>
+        <v>70.13915638921813</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576398900373104</v>
+        <v>1.576160817735239</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.535093556543517</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C2" t="n">
-        <v>2.721404636172158</v>
+        <v>8.066039138091794</v>
       </c>
       <c r="D2" t="n">
-        <v>16.70345544005523</v>
+        <v>24.34341607450391</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99190933865455</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="C3" t="n">
-        <v>8.595201150680825</v>
+        <v>24.02336632291945</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81733817374786</v>
+        <v>25.61870634232052</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.83853571261379</v>
+        <v>10.771735810996</v>
       </c>
       <c r="C4" t="n">
-        <v>12.99244911800229</v>
+        <v>37.66278717802039</v>
       </c>
       <c r="D4" t="n">
-        <v>19.32275831498572</v>
+        <v>22.44962475301181</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44611234051997</v>
+        <v>15.43867595539074</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17304779447983</v>
+        <v>86.13156059323258</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251813124319994</v>
+        <v>3.250247569555946</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.372123437638546</v>
+        <v>4.957825906446392</v>
       </c>
       <c r="C2" t="n">
-        <v>2.874557278034661</v>
+        <v>5.065818153913542</v>
       </c>
       <c r="D2" t="n">
-        <v>20.49594682156066</v>
+        <v>39.03919745937441</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15880644837651</v>
+        <v>15.53615741970577</v>
       </c>
       <c r="C3" t="n">
-        <v>9.827294519510573</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="D3" t="n">
-        <v>26.27647730416588</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.05245890114836</v>
+        <v>23.4834050855837</v>
       </c>
       <c r="C4" t="n">
-        <v>18.11029990024091</v>
+        <v>50.32340557198725</v>
       </c>
       <c r="D4" t="n">
-        <v>23.22815068247953</v>
+        <v>30.23488404768902</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.94081740030471</v>
+        <v>9.817477042468106</v>
       </c>
       <c r="C5" t="n">
-        <v>16.1742934274662</v>
+        <v>41.94517066394498</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74742589742382</v>
+        <v>16.72844006636194</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1592979742853</v>
+        <v>102.0434844048078</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024227769227148</v>
+        <v>4.182110016590484</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.853179812719484</v>
+        <v>5.10017932356218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.861213720802705</v>
+        <v>12.2649740691554</v>
       </c>
       <c r="D2" t="n">
-        <v>24.49460522095792</v>
+        <v>37.98676392042183</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.80046853632642</v>
+        <v>16.26755945936965</v>
       </c>
       <c r="C3" t="n">
-        <v>10.60778394438679</v>
+        <v>23.40977400776519</v>
       </c>
       <c r="D3" t="n">
-        <v>36.00559705325177</v>
+        <v>60.10750319251097</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.27241144462865</v>
+        <v>26.82723776624834</v>
       </c>
       <c r="C4" t="n">
-        <v>21.62004794292326</v>
+        <v>61.19724314422493</v>
       </c>
       <c r="D4" t="n">
-        <v>30.51566389110361</v>
+        <v>42.35946819513713</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.2252464970958</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C5" t="n">
-        <v>25.84450831429729</v>
+        <v>69.48319376806802</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>34.21390749300135</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59876828859932</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>19.48180144307371</v>
+        <v>40.33215918586747</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>46.09305471438775</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08664517696571</v>
+        <v>18.04569312606939</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9938280592525</v>
+        <v>117.7266646795955</v>
       </c>
       <c r="D21" t="n">
-        <v>6.890150543605983</v>
+        <v>6.015231042023129</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.453027660014286</v>
+        <v>5.538038799656257</v>
       </c>
       <c r="C2" t="n">
-        <v>3.91815508764902</v>
+        <v>9.010480429577225</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92577238957152</v>
+        <v>28.47264691856599</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5585576904542</v>
+        <v>14.99128744384879</v>
       </c>
       <c r="C3" t="n">
-        <v>12.45346962837079</v>
+        <v>34.76368620737956</v>
       </c>
       <c r="D3" t="n">
-        <v>44.50262343350792</v>
+        <v>71.12762117268142</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.81898287398687</v>
+        <v>21.14782729718054</v>
       </c>
       <c r="C4" t="n">
-        <v>20.53521672973053</v>
+        <v>49.91499852702059</v>
       </c>
       <c r="D4" t="n">
-        <v>36.43756604312036</v>
+        <v>54.01183169684252</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.20008090968388</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C5" t="n">
-        <v>24.91184799526282</v>
+        <v>68.10874698212248</v>
       </c>
       <c r="D5" t="n">
-        <v>28.81429511964389</v>
+        <v>33.20761609614836</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24908617943821</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>21.21262264566084</v>
+        <v>51.64287448649497</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>31.51704654943536</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>16.04961146902685</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.075689143041189</v>
+        <v>7.048361417550884</v>
       </c>
       <c r="C21" t="n">
-        <v>67.21904685889129</v>
+        <v>66.07838828953955</v>
       </c>
       <c r="D21" t="n">
-        <v>5.306766857280892</v>
+        <v>4.405225885969303</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.811946409141117</v>
+        <v>4.894994053374596</v>
       </c>
       <c r="C2" t="n">
-        <v>5.519385593275567</v>
+        <v>8.877944489503905</v>
       </c>
       <c r="D2" t="n">
-        <v>19.21771131063131</v>
+        <v>32.21703266256333</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.92595231602077</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C3" t="n">
-        <v>14.40714755982194</v>
+        <v>35.02384934900495</v>
       </c>
       <c r="D3" t="n">
-        <v>53.4954324044087</v>
+        <v>77.8575016852933</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.72812230584842</v>
+        <v>26.26567807941916</v>
       </c>
       <c r="C4" t="n">
-        <v>27.60576369571606</v>
+        <v>72.96447112732719</v>
       </c>
       <c r="D4" t="n">
-        <v>51.71454206890498</v>
+        <v>78.75874607779187</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>26.55627539987623</v>
       </c>
       <c r="C5" t="n">
-        <v>33.33033455917922</v>
+        <v>82.73678777539996</v>
       </c>
       <c r="D5" t="n">
-        <v>36.64373306101221</v>
+        <v>45.43037501402116</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.64030479181395</v>
+        <v>19.20003985195487</v>
       </c>
       <c r="C6" t="n">
-        <v>32.60384125803657</v>
+        <v>84.44797402390215</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.6360747013607</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15237618280328</v>
+        <v>53.23919625360028</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>20.61179305066178</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.308622516777824</v>
+        <v>7.264999556874012</v>
       </c>
       <c r="C21" t="n">
-        <v>77.65411424076439</v>
+        <v>75.37437040256789</v>
       </c>
       <c r="D21" t="n">
-        <v>6.395044702180596</v>
+        <v>5.44874966765551</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.177737392197677</v>
+        <v>3.594178345247573</v>
       </c>
       <c r="C2" t="n">
-        <v>8.319330045787471</v>
+        <v>6.148685871697774</v>
       </c>
       <c r="D2" t="n">
-        <v>20.88471891244239</v>
+        <v>27.77462430084651</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.64615422031042</v>
+        <v>17.36220814960484</v>
       </c>
       <c r="C3" t="n">
-        <v>18.94282195344221</v>
+        <v>34.69496386808228</v>
       </c>
       <c r="D3" t="n">
-        <v>56.710656135817</v>
+        <v>85.02425992629502</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.61173629739955</v>
+        <v>30.45185029032756</v>
       </c>
       <c r="C4" t="n">
-        <v>32.62151271671301</v>
+        <v>81.3495782692992</v>
       </c>
       <c r="D4" t="n">
-        <v>67.74451858384691</v>
+        <v>98.15808071370884</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.60155896745859</v>
+        <v>33.28124717396688</v>
       </c>
       <c r="C5" t="n">
-        <v>44.20319038371264</v>
+        <v>110.6184225760094</v>
       </c>
       <c r="D5" t="n">
-        <v>47.22206457427158</v>
+        <v>63.37181430913162</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>44.67933802027235</v>
+        <v>110.048027159842</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>41.33845058272045</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>16.40893112878119</v>
       </c>
       <c r="C7" t="n">
-        <v>38.14777054391831</v>
+        <v>90.06946137841938</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>28.37250865273282</v>
+        <v>50.06913291658733</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.532843727501826</v>
+        <v>7.46689266701581</v>
       </c>
       <c r="C21" t="n">
-        <v>87.56930833220872</v>
+        <v>84.00254250392787</v>
       </c>
       <c r="D21" t="n">
-        <v>7.532843727501826</v>
+        <v>6.533531083638834</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_29_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628244782</v>
+        <v>10.84497646999098</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890717684967</v>
+        <v>37.78907242198656</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.660356352059609</v>
+        <v>0.8305585577928015</v>
       </c>
       <c r="C2" t="n">
-        <v>5.201299337099601</v>
+        <v>1.622828955119977</v>
       </c>
       <c r="D2" t="n">
-        <v>34.69103687726529</v>
+        <v>11.8182788637231</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.60840583919254</v>
+        <v>7.142214548395545</v>
       </c>
       <c r="C3" t="n">
-        <v>28.77502521147402</v>
+        <v>23.23305942100077</v>
       </c>
       <c r="D3" t="n">
-        <v>86.9239417340126</v>
+        <v>59.77370897306705</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.97061398879738</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C4" t="n">
-        <v>83.2895117328909</v>
+        <v>99.34501368814324</v>
       </c>
       <c r="D4" t="n">
-        <v>116.408770535657</v>
+        <v>61.2993449054666</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C5" t="n">
-        <v>130.744250513069</v>
+        <v>140.4390090925062</v>
       </c>
       <c r="D5" t="n">
-        <v>81.28870991163591</v>
+        <v>40.07985002587604</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.54850353370026</v>
+        <v>8.734609324683873</v>
       </c>
       <c r="C6" t="n">
-        <v>141.4040670857809</v>
+        <v>90.28446412564944</v>
       </c>
       <c r="D6" t="n">
-        <v>50.95859633663495</v>
+        <v>28.69943063824701</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>124.6240353247943</v>
+        <v>45.27427712904591</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>83.53200341583985</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.653500112812806</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.79868886785528</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.653500112812806</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.20817157102933</v>
+        <v>0.5654866776461628</v>
       </c>
       <c r="C2" t="n">
-        <v>7.63014315740621</v>
+        <v>9.964739198105125</v>
       </c>
       <c r="D2" t="n">
-        <v>28.25077193740622</v>
+        <v>15.85031668506475</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92256510455152</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3473430653209</v>
+        <v>13.13087554430109</v>
       </c>
       <c r="D3" t="n">
-        <v>92.29410167624265</v>
+        <v>55.93016671094079</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>13.12007631955437</v>
       </c>
       <c r="C4" t="n">
-        <v>77.64838942428872</v>
+        <v>76.55079549094079</v>
       </c>
       <c r="D4" t="n">
-        <v>128.584405563726</v>
+        <v>76.60184637156163</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.65693774952392</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7517856995335</v>
+        <v>165.5717503212246</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7027707631166</v>
+        <v>52.30260894374884</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>171.5928089913703</v>
+        <v>159.1952989821416</v>
       </c>
       <c r="D6" t="n">
-        <v>61.62528514327655</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4780423209646</v>
+        <v>89.77002832862408</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.85937339858123</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>120.5831617741145</v>
+        <v>44.72842540548468</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>70.88905648054941</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.823669950991503</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7297506190156</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.801628694865441</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.902267197931824</v>
+        <v>0.2935425635697963</v>
       </c>
       <c r="C2" t="n">
-        <v>7.691011515069513</v>
+        <v>4.09683316982194</v>
       </c>
       <c r="D2" t="n">
-        <v>23.79756435094269</v>
+        <v>10.69515949006475</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.63433219013045</v>
+        <v>4.069344234103029</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44337441388784</v>
+        <v>26.96370069713865</v>
       </c>
       <c r="D3" t="n">
-        <v>92.25974050659401</v>
+        <v>57.39297079026854</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.4098150654942</v>
+        <v>14.3580601746096</v>
       </c>
       <c r="C4" t="n">
-        <v>69.36538404355839</v>
+        <v>65.61314431792708</v>
       </c>
       <c r="D4" t="n">
-        <v>140.7089897111741</v>
+        <v>85.86758120424302</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.09872421643498</v>
+        <v>14.87347771933918</v>
       </c>
       <c r="C5" t="n">
-        <v>139.3590866178347</v>
+        <v>180.8379271222625</v>
       </c>
       <c r="D5" t="n">
-        <v>116.3616466458532</v>
+        <v>60.52474596681587</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.90576188705487</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>192.765179981157</v>
+        <v>203.230610508428</v>
       </c>
       <c r="D6" t="n">
-        <v>74.7070733023653</v>
+        <v>35.34095385747668</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.3036885024443</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>194.451822537053</v>
+        <v>84.02091377255476</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>157.1336288032232</v>
+        <v>42.22496875965531</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>102.5062412958179</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>58.93431468593603</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.97843713680231</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7089013468312</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.973046421002888</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.446736263161304</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="C2" t="n">
-        <v>5.352488483553611</v>
+        <v>6.524695242424301</v>
       </c>
       <c r="D2" t="n">
-        <v>19.92358790998477</v>
+        <v>11.36274792895258</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03117924682442</v>
+        <v>2.444551783574558</v>
       </c>
       <c r="C3" t="n">
-        <v>40.65417243286042</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="D3" t="n">
-        <v>100.7616756253714</v>
+        <v>52.75421288770235</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.70113209174825</v>
+        <v>11.26948189704914</v>
       </c>
       <c r="C4" t="n">
-        <v>106.8494931394059</v>
+        <v>67.2850606582594</v>
       </c>
       <c r="D4" t="n">
-        <v>133.6767309056542</v>
+        <v>95.63106212297755</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.53802310412304</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C5" t="n">
-        <v>115.1835494007571</v>
+        <v>150.9927969131595</v>
       </c>
       <c r="D5" t="n">
-        <v>75.91364123088462</v>
+        <v>75.74183538264143</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.99627829782805</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C6" t="n">
-        <v>128.0807689914474</v>
+        <v>249.8822796665322</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76484788153306</v>
+        <v>44.67933802027235</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>110.4907953744573</v>
+        <v>184.0315524041773</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>75.52094214918588</v>
+        <v>74.18576527141022</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>44.92968368485526</v>
+        <v>38.162496759482</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>24.00864010735575</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.308489763311751</v>
+        <v>0.3475386873033709</v>
       </c>
       <c r="C2" t="n">
-        <v>2.627156856564465</v>
+        <v>2.905973204570559</v>
       </c>
       <c r="D2" t="n">
-        <v>14.18723607407066</v>
+        <v>9.424777960769379</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3600647277471</v>
+        <v>2.208932334555323</v>
       </c>
       <c r="C3" t="n">
-        <v>31.38647410477053</v>
+        <v>23.45886139297754</v>
       </c>
       <c r="D3" t="n">
-        <v>95.76948854927636</v>
+        <v>50.26548245743669</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.31222113214627</v>
+        <v>8.857327787714723</v>
       </c>
       <c r="C4" t="n">
-        <v>108.202341475858</v>
+        <v>61.51631114810513</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3621139764055</v>
+        <v>100.0086751362141</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.50780990946964</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C5" t="n">
-        <v>152.7353990881975</v>
+        <v>144.5132620651305</v>
       </c>
       <c r="D5" t="n">
-        <v>98.3956636581366</v>
+        <v>89.41267216427826</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>156.3374314150791</v>
+        <v>259.3011671410761</v>
       </c>
       <c r="D6" t="n">
-        <v>41.25794727097221</v>
+        <v>53.81646390369741</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>139.4759145946401</v>
+        <v>255.4163914753714</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>99.63757450400877</v>
+        <v>118.1631536831461</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>50.9203081761693</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.336379609658161</v>
+        <v>0.5969026041820606</v>
       </c>
       <c r="C2" t="n">
-        <v>11.90270916628833</v>
+        <v>8.598146393793566</v>
       </c>
       <c r="D2" t="n">
-        <v>19.22360179685679</v>
+        <v>15.08357172804799</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.45270886484479</v>
+        <v>1.693514789825748</v>
       </c>
       <c r="C3" t="n">
-        <v>20.42035224833366</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="D3" t="n">
-        <v>85.95201150680825</v>
+        <v>46.45630136495907</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.57496966398591</v>
+        <v>6.598326320242813</v>
       </c>
       <c r="C4" t="n">
-        <v>93.1806198531775</v>
+        <v>59.9720220093249</v>
       </c>
       <c r="D4" t="n">
-        <v>161.0782910788869</v>
+        <v>101.9741340401162</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C5" t="n">
-        <v>176.5182372235765</v>
+        <v>130.5479009722196</v>
       </c>
       <c r="D5" t="n">
-        <v>124.3874341280709</v>
+        <v>102.494460323367</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.61642405174254</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>195.5022925805971</v>
+        <v>246.9439087877215</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>66.45548384817086</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>13.53437385074653</v>
       </c>
       <c r="C7" t="n">
-        <v>180.0191495369206</v>
+        <v>313.9854960153276</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>137.6901155206152</v>
+        <v>214.7965802121596</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>79.43124325520091</v>
+        <v>90.85780478492953</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.569233742013903</v>
+        <v>0.4005530633326986</v>
       </c>
       <c r="C2" t="n">
-        <v>5.649958037940394</v>
+        <v>4.471860792844222</v>
       </c>
       <c r="D2" t="n">
-        <v>13.43325383720911</v>
+        <v>10.86009310437822</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>2.513274122871834</v>
       </c>
       <c r="C3" t="n">
-        <v>32.65292864324891</v>
+        <v>25.54998400302324</v>
       </c>
       <c r="D3" t="n">
-        <v>85.08316478854982</v>
+        <v>52.51368470016189</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.56144618030471</v>
+        <v>11.30777005751476</v>
       </c>
       <c r="C4" t="n">
-        <v>87.47568394379931</v>
+        <v>82.35783316156066</v>
       </c>
       <c r="D4" t="n">
-        <v>169.9228561464464</v>
+        <v>104.7564070339517</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.88916998707391</v>
+        <v>13.42539985557513</v>
       </c>
       <c r="C5" t="n">
-        <v>206.9769597478339</v>
+        <v>202.1418523044183</v>
       </c>
       <c r="D5" t="n">
-        <v>130.9406000539184</v>
+        <v>94.81228453763572</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.2566624236317</v>
+        <v>8.372344421816802</v>
       </c>
       <c r="C6" t="n">
-        <v>229.5954451059761</v>
+        <v>267.3112466600258</v>
       </c>
       <c r="D6" t="n">
-        <v>56.27181491201868</v>
+        <v>58.56615929684348</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>184.2112122340545</v>
+        <v>151.0340303167378</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>98.96998606512095</v>
+        <v>66.92574099850506</v>
       </c>
       <c r="D8" t="n">
         <v>31.12631096314512</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.770492021384499</v>
+        <v>0.2130392518215578</v>
       </c>
       <c r="C2" t="n">
-        <v>7.601672473983053</v>
+        <v>2.254092728950677</v>
       </c>
       <c r="D2" t="n">
-        <v>17.99641716654828</v>
+        <v>8.468555696832986</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.79217258633594</v>
+        <v>1.948769192929919</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37112599440108</v>
+        <v>21.12230185687012</v>
       </c>
       <c r="D3" t="n">
-        <v>77.74460069930491</v>
+        <v>49.00393665747954</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.96610616090365</v>
+        <v>7.606581212504287</v>
       </c>
       <c r="C4" t="n">
-        <v>85.30602151741385</v>
+        <v>69.69721476759382</v>
       </c>
       <c r="D4" t="n">
-        <v>172.6285528193506</v>
+        <v>102.5995073277214</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="C5" t="n">
-        <v>185.9184714917398</v>
+        <v>160.8348176482337</v>
       </c>
       <c r="D5" t="n">
-        <v>155.1406809636022</v>
+        <v>98.42020735074277</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>8.090582830697967</v>
       </c>
       <c r="C6" t="n">
-        <v>277.3339089726815</v>
+        <v>245.5753524880014</v>
       </c>
       <c r="D6" t="n">
-        <v>77.36368259005717</v>
+        <v>62.18880832551422</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.4507453694363</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>246.0740803217588</v>
+        <v>186.4270168025396</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>156.4660403643354</v>
+        <v>79.02578145334699</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.827032477603314</v>
+        <v>0.3013965452037708</v>
       </c>
       <c r="C2" t="n">
-        <v>4.778166076569226</v>
+        <v>10.24257379840697</v>
       </c>
       <c r="D2" t="n">
-        <v>13.44307131425157</v>
+        <v>9.902889092737576</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.50608309377262</v>
+        <v>1.276272015520854</v>
       </c>
       <c r="C3" t="n">
-        <v>28.57376693210342</v>
+        <v>13.63156687346696</v>
       </c>
       <c r="D3" t="n">
-        <v>75.00552460445631</v>
+        <v>44.40935740160447</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>5.564545987670921</v>
       </c>
       <c r="C4" t="n">
-        <v>80.41789969796898</v>
+        <v>60.53358169615408</v>
       </c>
       <c r="D4" t="n">
-        <v>172.7178918604371</v>
+        <v>104.2331355075881</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.55938487390499</v>
+        <v>12.14912784005428</v>
       </c>
       <c r="C5" t="n">
-        <v>179.8316357254095</v>
+        <v>143.0651842013665</v>
       </c>
       <c r="D5" t="n">
-        <v>172.0758288618597</v>
+        <v>113.440947225719</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.54600025894403</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>299.9955912298107</v>
+        <v>254.6319750596782</v>
       </c>
       <c r="D6" t="n">
-        <v>91.53226545774713</v>
+        <v>78.45047729865838</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.83380690054181</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>297.9358845463008</v>
+        <v>275.7778388614503</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>201.9455027635689</v>
+        <v>166.5633155025138</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>70.9999939711293</v>
+        <v>65.89686940445439</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.700787934382975</v>
+        <v>0.1610066234964769</v>
       </c>
       <c r="C2" t="n">
-        <v>6.249805885235195</v>
+        <v>15.71974424039993</v>
       </c>
       <c r="D2" t="n">
-        <v>19.10579207234718</v>
+        <v>11.04662516818511</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.002626447943252</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C3" t="n">
-        <v>23.85156047467626</v>
+        <v>28.14179794223482</v>
       </c>
       <c r="D3" t="n">
-        <v>69.98879383575512</v>
+        <v>42.08752408106076</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.53369520267854</v>
+        <v>3.969205968269854</v>
       </c>
       <c r="C4" t="n">
-        <v>76.20620204675016</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D4" t="n">
-        <v>168.7997367727881</v>
+        <v>101.9996594804266</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.04396732917541</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>166.1607989437727</v>
+        <v>126.7681723108694</v>
       </c>
       <c r="D5" t="n">
-        <v>188.3482970597506</v>
+        <v>125.0255701358313</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.83154997215961</v>
+        <v>14.53084777055704</v>
       </c>
       <c r="C6" t="n">
-        <v>295.6081607395316</v>
+        <v>242.3552200180719</v>
       </c>
       <c r="D6" t="n">
-        <v>114.1536960590021</v>
+        <v>94.91340455117314</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>354.5287309576081</v>
+        <v>324.106333098408</v>
       </c>
       <c r="D7" t="n">
-        <v>55.21545438224911</v>
+        <v>53.71828913327272</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>272.8767743954009</v>
+        <v>264.615367464164</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>133.568738658187</v>
+        <v>132.9031137147077</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.304963683122264</v>
+        <v>3.208351497478576</v>
       </c>
       <c r="C2" t="n">
-        <v>9.664324400605601</v>
+        <v>9.52295273119406</v>
       </c>
       <c r="D2" t="n">
-        <v>13.03270077387641</v>
+        <v>6.21740821099505</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.950732688338412</v>
+        <v>0.2689988709636261</v>
       </c>
       <c r="C2" t="n">
-        <v>3.649156216685394</v>
+        <v>11.46877668101124</v>
       </c>
       <c r="D2" t="n">
-        <v>14.21374326208532</v>
+        <v>16.41776685811941</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.13931036301181</v>
+        <v>0.8393942871310229</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58220175081414</v>
+        <v>44.85605260703677</v>
       </c>
       <c r="D3" t="n">
-        <v>76.90029767365266</v>
+        <v>41.44938807330033</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>3.063052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>106.7091032176986</v>
+        <v>57.25356261626548</v>
       </c>
       <c r="D4" t="n">
-        <v>174.1983673984413</v>
+        <v>99.05147112457344</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.91246989006857</v>
+        <v>8.663923489978103</v>
       </c>
       <c r="C5" t="n">
-        <v>248.3576254818369</v>
+        <v>107.0595871481147</v>
       </c>
       <c r="D5" t="n">
-        <v>170.382314072034</v>
+        <v>132.1432409916207</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.77864910265474</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>288.5641209615608</v>
+        <v>222.79291526325</v>
       </c>
       <c r="D6" t="n">
-        <v>86.42030516173399</v>
+        <v>108.5587158924996</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C7" t="n">
-        <v>191.8766983088136</v>
+        <v>339.6768516877624</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>65.99504417487908</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>98.3858461810941</v>
+        <v>341.4714864911256</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>217.3265440460036</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>96.80032363873552</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.541384953396497</v>
+        <v>2.606540154775282</v>
       </c>
       <c r="C2" t="n">
-        <v>6.110397711232148</v>
+        <v>11.04171642966388</v>
       </c>
       <c r="D2" t="n">
-        <v>17.78632315783946</v>
+        <v>7.526077900756048</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.149888603580273</v>
+        <v>5.30634634145401</v>
       </c>
       <c r="C3" t="n">
-        <v>24.35225180384213</v>
+        <v>18.80046853632642</v>
       </c>
       <c r="D3" t="n">
-        <v>14.08317081742049</v>
+        <v>7.304202919596269</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39736695074953</v>
+        <v>11.67852732399711</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13915638921813</v>
+        <v>59.9497735965185</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576160817735239</v>
+        <v>0.778568488266474</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.122358610132356</v>
+        <v>1.799543541884403</v>
       </c>
       <c r="C2" t="n">
-        <v>8.066039138091794</v>
+        <v>9.871473166201678</v>
       </c>
       <c r="D2" t="n">
-        <v>24.34341607450391</v>
+        <v>11.08589507635498</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16094987023424</v>
+        <v>7.706719478337462</v>
       </c>
       <c r="C3" t="n">
-        <v>24.02336632291945</v>
+        <v>35.02384934900495</v>
       </c>
       <c r="D3" t="n">
-        <v>25.61870634232052</v>
+        <v>12.09022297779947</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.771735810996</v>
+        <v>6.71319080163969</v>
       </c>
       <c r="C4" t="n">
-        <v>37.66278717802039</v>
+        <v>31.1027490182432</v>
       </c>
       <c r="D4" t="n">
-        <v>22.44962475301181</v>
+        <v>17.99543541884404</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43867595539074</v>
+        <v>13.63172181474349</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13156059323258</v>
+        <v>73.77167099743534</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250247569555946</v>
+        <v>1.603731978205116</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.957825906446392</v>
+        <v>1.32045066221196</v>
       </c>
       <c r="C2" t="n">
-        <v>5.065818153913542</v>
+        <v>4.548437113775472</v>
       </c>
       <c r="D2" t="n">
-        <v>39.03919745937441</v>
+        <v>20.5892128534641</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.53615741970577</v>
+        <v>6.891868883812609</v>
       </c>
       <c r="C3" t="n">
-        <v>28.39705234533899</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D3" t="n">
-        <v>39.14718970684157</v>
+        <v>18.47649179392497</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.4834050855837</v>
+        <v>11.72893982263664</v>
       </c>
       <c r="C4" t="n">
-        <v>50.32340557198725</v>
+        <v>66.71073825127502</v>
       </c>
       <c r="D4" t="n">
-        <v>30.23488404768902</v>
+        <v>19.97365704290135</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.817477042468106</v>
+        <v>6.626797003665971</v>
       </c>
       <c r="C5" t="n">
-        <v>41.94517066394498</v>
+        <v>37.01188845010476</v>
       </c>
       <c r="D5" t="n">
-        <v>30.72870314292517</v>
+        <v>26.55627539987623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72844006636194</v>
+        <v>14.84518756963135</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0434844048078</v>
+        <v>87.42166013227353</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182110016590484</v>
+        <v>2.474197928271892</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.10017932356218</v>
+        <v>1.73278469799562</v>
       </c>
       <c r="C2" t="n">
-        <v>12.2649740691554</v>
+        <v>6.277294820954105</v>
       </c>
       <c r="D2" t="n">
-        <v>37.98676392042183</v>
+        <v>29.04893282095887</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26755945936965</v>
+        <v>5.576326960121883</v>
       </c>
       <c r="C3" t="n">
-        <v>23.40977400776519</v>
+        <v>25.24564221470673</v>
       </c>
       <c r="D3" t="n">
-        <v>60.10750319251097</v>
+        <v>30.65998080362789</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.82723776624834</v>
+        <v>12.82653375598458</v>
       </c>
       <c r="C4" t="n">
-        <v>61.19724314422493</v>
+        <v>82.77900292668257</v>
       </c>
       <c r="D4" t="n">
-        <v>42.35946819513713</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.48202242725196</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>69.48319376806802</v>
+        <v>87.05647767408593</v>
       </c>
       <c r="D5" t="n">
-        <v>34.21390749300135</v>
+        <v>28.00435326364027</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.579894098040377</v>
+        <v>6.883033154474389</v>
       </c>
       <c r="C6" t="n">
-        <v>40.33215918586747</v>
+        <v>37.31328499530853</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04569312606939</v>
+        <v>16.09034475636609</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7266646795955</v>
+        <v>101.6232300402069</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015231042023129</v>
+        <v>3.387441001340229</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.538038799656257</v>
+        <v>2.050870954171587</v>
       </c>
       <c r="C2" t="n">
-        <v>9.010480429577225</v>
+        <v>5.10017932356218</v>
       </c>
       <c r="D2" t="n">
-        <v>28.47264691856599</v>
+        <v>25.81898287398687</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.99128744384879</v>
+        <v>5.772676500971246</v>
       </c>
       <c r="C3" t="n">
-        <v>34.76368620737956</v>
+        <v>24.72040719293469</v>
       </c>
       <c r="D3" t="n">
-        <v>71.12762117268142</v>
+        <v>45.91634012762332</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.14782729718054</v>
+        <v>11.80551614356789</v>
       </c>
       <c r="C4" t="n">
-        <v>49.91499852702059</v>
+        <v>71.84135175366885</v>
       </c>
       <c r="D4" t="n">
-        <v>54.01183169684252</v>
+        <v>33.85949657176824</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.21771131063132</v>
+        <v>15.9288565014045</v>
       </c>
       <c r="C5" t="n">
-        <v>68.10874698212248</v>
+        <v>121.7858027118169</v>
       </c>
       <c r="D5" t="n">
-        <v>33.20761609614836</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>51.64287448649497</v>
+        <v>90.52597406089416</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>35.38120551335081</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>25.21226279276233</v>
+        <v>36.47094546506476</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048361417550884</v>
+        <v>17.35958479228295</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07838828953955</v>
+        <v>115.4412388686816</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405225885969303</v>
+        <v>4.339896198070737</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.894994053374596</v>
+        <v>1.778926840095221</v>
       </c>
       <c r="C2" t="n">
-        <v>8.877944489503905</v>
+        <v>5.594980166502572</v>
       </c>
       <c r="D2" t="n">
-        <v>32.21703266256333</v>
+        <v>21.19495118698439</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64691498383642</v>
+        <v>6.361725123519332</v>
       </c>
       <c r="C3" t="n">
-        <v>35.02384934900495</v>
+        <v>21.96169614400115</v>
       </c>
       <c r="D3" t="n">
-        <v>77.8575016852933</v>
+        <v>54.73243451175968</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>11.3588209381356</v>
       </c>
       <c r="C4" t="n">
-        <v>72.96447112732719</v>
+        <v>66.49377200863647</v>
       </c>
       <c r="D4" t="n">
-        <v>78.75874607779187</v>
+        <v>47.60494617892783</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.55627539987623</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>82.73678777539996</v>
+        <v>127.2590461629928</v>
       </c>
       <c r="D5" t="n">
-        <v>45.43037501402116</v>
+        <v>34.68023765251858</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.20003985195487</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>84.44797402390215</v>
+        <v>140.0757624419349</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46170882509904</v>
+        <v>37.19253002768617</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>53.23919625360028</v>
+        <v>82.64352174349649</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53802310412303</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264999556874012</v>
+        <v>17.76005050533726</v>
       </c>
       <c r="C21" t="n">
-        <v>75.37437040256789</v>
+        <v>128.7603661636951</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44874966765551</v>
+        <v>5.328015151601178</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.594178345247573</v>
+        <v>1.628719441345458</v>
       </c>
       <c r="C2" t="n">
-        <v>6.148685871697774</v>
+        <v>3.445934441906304</v>
       </c>
       <c r="D2" t="n">
-        <v>27.77462430084651</v>
+        <v>16.65731329795563</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36220814960484</v>
+        <v>8.109236037078654</v>
       </c>
       <c r="C3" t="n">
-        <v>34.69496386808228</v>
+        <v>34.82259106963436</v>
       </c>
       <c r="D3" t="n">
-        <v>85.02425992629502</v>
+        <v>59.13066422678538</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>8.155378179178253</v>
       </c>
       <c r="C4" t="n">
-        <v>81.3495782692992</v>
+        <v>105.0116614370558</v>
       </c>
       <c r="D4" t="n">
-        <v>98.15808071370884</v>
+        <v>44.38874069981528</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.28124717396688</v>
+        <v>9.302059497738529</v>
       </c>
       <c r="C5" t="n">
-        <v>110.6184225760094</v>
+        <v>83.6939917870406</v>
       </c>
       <c r="D5" t="n">
-        <v>63.37181430913162</v>
+        <v>32.54493639578177</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>6.722026530977913</v>
       </c>
       <c r="C6" t="n">
-        <v>110.048027159842</v>
+        <v>54.42023874180921</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>25.318291544821</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.40893112878119</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>90.06946137841938</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>50.06913291658733</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46689266701581</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.00254250392787</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.533531083638834</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
